--- a/12_ai-governance-operating-model/exercises/starter/ai_governance_core.xlsx
+++ b/12_ai-governance-operating-model/exercises/starter/ai_governance_core.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Govern Crosswalk" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Mode Stress Test" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iteration Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -163,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -233,6 +234,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -598,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -677,6 +679,20 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>REASONING NOTE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>For every cell where you fill in [Your response here], append a short rationale on a new line in the same cell, formatted as: Reasoning: &lt;one sentence on why this design choice is the right one&gt;. This applies across the Charter, RACI Matrix (including the Reasoning notes block), Reporting Cadence, Red-Team Governance, Govern Crosswalk, Failure Mode Stress Test, and Iteration Log. Use Alt+Enter (Mac: Option+Enter) for a soft line break inside a cell. This rationale is part of the deliverable — graders look for it.</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
@@ -716,6 +732,55 @@
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Yellow — Reference / rubric (read-only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>CAPSTONE CROSS-REFERENCES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>This capstone integrates artifacts from earlier modules. As you fill the sheets, reference your prior work:</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>• Charter §1 Scope and Govern Crosswalk: ties to M4 (EU AI Act Compliance Matrix) and M9 (Article 11 Crosswalk). The launch-approval scope here should align with what your Article 11 Crosswalk treated as in-scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>• RACI #1 Launch approval: ties to M3 (Threat Model + Board Brief) and M2 (NIST AI RMF Risk Register). The Accountable role here should be consistent with the owner you named in those prior workbooks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>• RACI #4 Incident escalation + Reporting Cadence: ties to M6 (Incident Response Playbook) escalation paths and M7 (KRI dashboard) thresholds. The S2+ trigger here should match your S1/S2 SLAs from M6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>• RACI #5 Jailbreak red-team commissioning and Red-Team Governance: ties to M3 (MITRE ATLAS Threat Model). The TTPs you scoped in M3 (AML.T0051, AML.T0015) are the same ones the red-team would target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>• Failure Mode Stress Test: pulls from M5 (AI Policy / AUP). The AUP body's enforcement mechanisms are what the stress test is probing for — 'Governance on paper' specifically asks whether your M5 AUP has measurable controls.</t>
         </is>
       </c>
     </row>
@@ -785,7 +850,7 @@
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>[Your response here — write the section. See the pre-filled sections 1 and 5 for tone and depth.]</t>
+          <t>[Your response here — write the Membership section body. Specify the chair role, named voting members (tied to MegaShop's 12 AI use cases and 9 markets), non-voting advisors/observers, and a secretary; follow the depth and structure of the pre-filled §1 Scope and §5 Reporting Outputs.]</t>
         </is>
       </c>
     </row>
@@ -802,7 +867,7 @@
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>[Your response here — write the section. See the pre-filled sections 1 and 5 for tone and depth.]</t>
+          <t>[Your response here — write the Decision Rights section body. List which decision categories the AIRB owns versus what is delegated (launch approval, vendor onboarding, retraining, incident escalation, red-team) and keep it internally consistent with the RACI Matrix rows.]</t>
         </is>
       </c>
     </row>
@@ -819,7 +884,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>[Your response here — write the section. See the pre-filled sections 1 and 5 for tone and depth.]</t>
+          <t>[Your response here — write the Cadence and Quorum section body. Set standing meeting frequency, ad-hoc/emergency triggers, and a quorum rule with tie-breaking; ensure the math is consistent with §2 Membership and the Reporting Cadence sheet.]</t>
         </is>
       </c>
     </row>
@@ -851,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1029,42 +1094,42 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="G4" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="J4" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
     </row>
@@ -1079,42 +1144,42 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="J5" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
     </row>
@@ -1129,104 +1194,110 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
         </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Your response here — assign R, A, C, or I for this role on this decision. Each decision row must have exactly one A; reference the legend at the bottom of the sheet.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Reasoning notes (your work area):</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Legend:</t>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Retraining sign-off (standard cadence)</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>[Your response here — explain WHO you assigned Accountable for retraining sign-off and WHY. Standard cadence is lower-risk than incident-driven retraining; your A vs R/C/I choices should reflect that.]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>R = Responsible (does the work)</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="18" t="n"/>
-      <c r="G9" s="18" t="n"/>
-      <c r="H9" s="18" t="n"/>
-      <c r="I9" s="18" t="n"/>
-      <c r="J9" s="19" t="n"/>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Incident escalation (S2+)</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>[Your response here — explain who you put on the critical path during an S2+ incident and why. M6 incident playbooks set the SLA; the RACI here implements who acts.]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>A = Accountable (owns outcome)</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="18" t="n"/>
-      <c r="G10" s="18" t="n"/>
-      <c r="H10" s="18" t="n"/>
-      <c r="I10" s="18" t="n"/>
-      <c r="J10" s="19" t="n"/>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jailbreak red-team commissioning + remediation sign-off</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>[Your response here — explain who commissions vs. who signs off on remediation. Separation-of-duties matters: the commissioner should not be the sign-off authority. Reference your M3 ATLAS scoping.]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>C = Consulted (input before)</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="18" t="n"/>
-      <c r="H11" s="18" t="n"/>
-      <c r="I11" s="18" t="n"/>
-      <c r="J11" s="19" t="n"/>
+      <c r="A11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>I = Informed (told after)</t>
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Legend:</t>
         </is>
       </c>
       <c r="B12" s="18" t="n"/>
@@ -1239,12 +1310,77 @@
       <c r="I12" s="18" t="n"/>
       <c r="J12" s="19" t="n"/>
     </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>R = Responsible (does the work)</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="19" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>A = Accountable (owns outcome)</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>C = Consulted (input before)</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="19" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>I = Informed (told after)</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="19" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A9:J9"/>
+  <mergeCells count="5">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:J15"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A13:J13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1336,17 +1472,17 @@
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — list 4-6 bullet points appropriate for a quarterly Board Audit Committee report (model portfolio status across the 12 use cases, incident summary, KRI trends, open risk acceptances, cross-BU governance issues). Reference the M7 KRI dashboard depth and follow the bullet style of the pre-filled Monthly row.]</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the role accountable for producing and presenting this quarterly report.]</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the deliverable format and meeting shape (e.g., deck length, accompanying meeting); calibrate to a board-audit-committee audience.]</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1499,17 @@
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — list 4-6 bullet points appropriate for an annual regulator-facing report (Article 11 documentation index, NIST AI RMF Govern crosswalk, impact assessments, red-team summary, maturity self-assessment). Follow the bullet style of the pre-filled Monthly row.]</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the role(s) accountable for producing the annual regulator-facing pack.]</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the deliverable format suitable for an external regulator (e.g., a bound PDF risk pack).]</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1564,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>[Your response here — bullets only; full procedure is out of scope.]</t>
+          <t>[Your response here — bullets only. Name where red-team findings flow (AIRB Chair? Model Owner? security/incident response?), the SLA for opening a tracked register entry, and any paging rule for Critical findings. Reference M6 incident playbook escalation paths.]</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1576,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>[Your response here — bullets only; full procedure is out of scope.]</t>
+          <t>[Your response here — bullets only. Name who signs off red-team remediation closure, what evidence is required to close, and what posture (block / waiver) applies while findings are open. Separation-of-duties matters: the commissioner should not also be the sole closer.]</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1588,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>[Your response here — bullets only; full procedure is out of scope.]</t>
+          <t>[Your response here — bullets only. Set red-team frequency for the 12 customer-affecting systems and the triggering events (S2+ incidents, major retrains, new attack-surface introduction); consider quarterly tabletop versus annual full engagement.]</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1663,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the NIST AI 100-1 Govern subcategory ID (e.g., Govern 2.x) that most precisely covers documented roles, responsibilities, and lines of communication for AI risks. See Reference Notes for closest-anchor guidance.]</t>
         </is>
       </c>
       <c r="C3" s="23" t="inlineStr">
@@ -1537,7 +1673,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — one to two sentences explaining how your Charter §2 Membership design (named chair, voting members, observers) satisfies the cited NIST subcategory and ISO A.3.2 control.]</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1685,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the NIST AI 100-1 Govern subcategory that most precisely covers AI-risk role competence / decision authorities (e.g., Govern 2.x). See Reference Notes for closest-anchor guidance.]</t>
         </is>
       </c>
       <c r="C4" s="23" t="inlineStr">
@@ -1559,7 +1695,7 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — one to two sentences explaining how your Charter §3 Decision Rights satisfies the cited NIST subcategory plus ISO A.3.2 / A.6.1.2 (what each role approves, recommends, or is informed of).]</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1729,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the NIST AI 100-1 Govern subcategory that most precisely covers third-party AI risk policies and procedures (Govern 6.x family). See Reference Notes for the Govern 6.1 vs 6.2 distinction.]</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -1603,7 +1739,7 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — one to two sentences explaining how your RACI #1 / #2 vendor onboarding design satisfies the cited NIST subcategory plus ISO A.10.2 (the supplier oversight loop for AI providers).]</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1751,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the NIST AI 100-1 Govern subcategory that most precisely covers organizational practices for AI testing, incident identification, and information sharing (Govern 4.x family). See Reference Notes.]</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -1625,7 +1761,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — one to two sentences explaining how your Red-Team Governance commissioner design (independence from the BU under test) satisfies the cited NIST subcategory and ISO A.6.2.4 adversarial-testing control.]</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1795,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the NIST AI 100-1 Govern subcategory that most precisely covers evaluating the effectiveness of AI risk management (Govern 1.x family). See Reference Notes for the Govern 1.4 vs 1.5 distinction.]</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -1669,7 +1805,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — one to two sentences explaining how your Failure Mode Stress Test sheet satisfies the cited NIST subcategory plus ISO A.6.1.4 (producing written evidence the design has been challenged).]</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1853,12 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>[Your response here — name the cell / row / charter section in your design.]</t>
+          <t>[Your response here — name the specific cell, row, or charter section in your design where the 'governance on paper' failure would surface (e.g., 'Charter §3 + RACI #1 Launch approval'). Be specific enough that a reviewer can audit it.]</t>
         </is>
       </c>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>[Your response here — name the specific mechanism. List 2–4 mechanisms.]</t>
+          <t>[Your response here — name 2-4 specific mechanisms in your design that prevent this failure. Each must be a concrete control (a binding approval, an observer role, a measurable KRI, a separation-of-duties), not a generic principle.]</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1870,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>[Your response here — name the cell / row / charter section in your design.]</t>
+          <t>[Your response here — name the specific cell, row, or charter section where the 'decision bottleneck' failure would surface (e.g., 'RACI #3 Retraining sign-off + Charter §4 Cadence'). Be specific enough that a reviewer can audit it.]</t>
         </is>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>[Your response here — name the specific mechanism. List 2–4 mechanisms.]</t>
+          <t>[Your response here — name 2-4 specific mechanisms in your design that prevent this failure. Each must be a concrete control (a delegated approval, a named trigger threshold, an ad-hoc cadence rule), not a generic principle.]</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1826,22 +1962,22 @@
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name a second element you revised (Charter §, RACI #, or Crosswalk row; different from row 2 above).]</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe the v1 state of this element.]</t>
         </is>
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe the v2 state after the stress-test finding or capstone-review feedback.]</t>
         </is>
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which named failure mode or finding drove the change?]</t>
         </is>
       </c>
     </row>
@@ -1853,22 +1989,139 @@
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name a third element you revised (different from rows 2 and 3 above; consider Red-Team Governance or Failure Mode Stress Test responses).]</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe the v1 state of this element.]</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe the v2 state after the stress-test finding or capstone-review feedback.]</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which named failure mode or finding drove the change?]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>v1 → v2</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>[Your response here — name a fourth element you revised (different from the first three; can pull from Charter §1 Scope, Reporting Cadence, or a Govern Crosswalk row).]</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>[Your response here — describe the v1 state of this element as you originally wrote it.]</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>[Your response here — describe the v2 state after the stress-test finding or capstone-review feedback.]</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>[Your response here — which named failure mode or finding drove the change? Reference the Failure Mode Stress Test row or a peer-review comment.]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>Specification detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="110" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>ISO 42001 Annex A — supplier control</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>In ISO/IEC 42001:2023 Annex A, the supplier-management control sits at A.10.3 ("Suppliers") within Clause A.10 (Third-party and customer relationships). A.10.2 in the same clause is "Allocating responsibilities" and addresses how the organization allocates responsibilities for the AI system across its lifecycle. Where the Govern Crosswalk references A.10.2 in a vendor-onboarding context, the Suppliers control (A.10.3) is the closer ISO 42001 anchor; both controls can apply when supplier onboarding also involves dividing responsibilities across teams. Reference: ISMS.online A.10.3 Suppliers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="110" customHeight="1">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>ISO 42001 Annex A — incident reporting</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Operational incident-reporting controls in ISO 42001 sit primarily under Clause A.9 (Use of AI systems) and A.6.2 (AI system life cycle — operation and monitoring). Clause A.4 covers Resources for AI systems. A.4.6 'Human resources' addresses documentation of human competencies across the AI lifecycle (training, role assignments, accountability for AI decisions) — which is the role A.4.6 plays in the Crosswalk's red-team remediation sign-off. Where the Govern Crosswalk references A.4.6 for an incident-reporting context, A.6.2.6 (AI system operation and monitoring) and A.9.x are the closer anchors for incident detection and reporting per se.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="110" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>NIST AI RMF Govern 6.1 vs 6.2</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>NIST AI 100-1 Govern subcategory 6.1 = "Policies and procedures address AI risks from third-party entities." Govern 6.2 = "Contingency processes handle failures or incidents in third-party data or high-risk AI systems." Where the Govern Crosswalk maps internal reporting cadence to Govern 6.1 or stakeholder communication to Govern 6.2, the 6.x family's primary scope is third-party and contingency; broader stakeholder communication aligns with the Govern 5.x family ("Processes are in place for robust engagement with relevant AI actors") and reporting cadence within the organization aligns with Govern 1.x and 4.x. The 6.x mappings used here capture the third-party / external-vendor reporting view of those controls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="110" customHeight="1">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>NIST AI RMF Govern 1.4 vs 1.5</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Govern 1.4 = "Risk management process and outcomes are established through transparent policies, procedures, and other controls." Govern 1.5 = "Ongoing monitoring and periodic review of the risk management process and its outcomes are planned." Where the Crosswalk paraphrases Govern 1.4 as "evaluating effectiveness of AI risk management," the periodic-review framing aligns more precisely with Govern 1.5; both subcategories together cover policy + ongoing review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Authoritative references</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>NIST AI 100-1 Playbook: https://airc.nist.gov/airmf-resources/playbook/govern/  •  ISO/IEC 42001:2023 catalog: https://www.iso.org/standard/42001  •  ISMS.online Annex A reference: https://www.isms.online/iso-42001/annex-a-controls/</t>
         </is>
       </c>
     </row>

--- a/12_ai-governance-operating-model/exercises/starter/ai_governance_core.xlsx
+++ b/12_ai-governance-operating-model/exercises/starter/ai_governance_core.xlsx
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Govern 6.2 — Mechanisms exist to communicate to relevant stakeholders the impacts of AI.</t>
+          <t>Govern 4.2 — Organizational teams document the risks and potential impacts of the AI technology they design, develop, deploy, evaluate, and use, and they communicate about the impacts more broadly.</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>NIST AI 100-1 Govern subcategory 6.1 = "Policies and procedures address AI risks from third-party entities." Govern 6.2 = "Contingency processes handle failures or incidents in third-party data or high-risk AI systems." Where the Govern Crosswalk maps internal reporting cadence to Govern 6.1 or stakeholder communication to Govern 6.2, the 6.x family's primary scope is third-party and contingency; broader stakeholder communication aligns with the Govern 5.x family ("Processes are in place for robust engagement with relevant AI actors") and reporting cadence within the organization aligns with Govern 1.x and 4.x. The 6.x mappings used here capture the third-party / external-vendor reporting view of those controls.</t>
+          <t>NIST AI 100-1 Govern subcategory 6.1 = "Policies and procedures address AI risks from third-party entities." Govern 6.2 = "Contingency processes handle failures or incidents in third-party data or high-risk AI systems." Where the Govern Crosswalk maps internal reporting cadence to Govern 6.1 or stakeholder communication to Govern 6.2, the 6.x family's primary scope is third-party and contingency; broader stakeholder communication aligns with the Govern 5.x family ("Processes are in place for robust engagement with relevant AI actors") and reporting cadence within the organization aligns with Govern 1.x and 4.x. Rows that concern third-party / external-vendor contingencies map to the 6.x family; the internal reporting-cadence row maps to Govern 4.2 (impact communication).</t>
         </is>
       </c>
     </row>

--- a/12_ai-governance-operating-model/exercises/starter/ai_governance_core.xlsx
+++ b/12_ai-governance-operating-model/exercises/starter/ai_governance_core.xlsx
@@ -1734,12 +1734,12 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>A.10.2 Suppliers — assessment, due diligence, and ongoing oversight of AI providers.</t>
+          <t>A.10.3 Suppliers — assessment, due diligence, and ongoing oversight of AI providers.</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>[Your response here — one to two sentences explaining how your RACI #1 / #2 vendor onboarding design satisfies the cited NIST subcategory plus ISO A.10.2 (the supplier oversight loop for AI providers).]</t>
+          <t>[Your response here — one to two sentences explaining how your RACI #1 / #2 vendor onboarding design satisfies the cited NIST subcategory plus ISO A.10.3 (the supplier oversight loop for AI providers).]</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B2" s="21" t="inlineStr">
         <is>
-          <t>In ISO/IEC 42001:2023 Annex A, the supplier-management control sits at A.10.3 ("Suppliers") within Clause A.10 (Third-party and customer relationships). A.10.2 in the same clause is "Allocating responsibilities" and addresses how the organization allocates responsibilities for the AI system across its lifecycle. Where the Govern Crosswalk references A.10.2 in a vendor-onboarding context, the Suppliers control (A.10.3) is the closer ISO 42001 anchor; both controls can apply when supplier onboarding also involves dividing responsibilities across teams. Reference: ISMS.online A.10.3 Suppliers.</t>
+          <t>In ISO/IEC 42001:2023 Annex A, the supplier-management control sits at A.10.3 ("Suppliers") within Clause A.10 (Third-party and customer relationships). A.10.2 in the same clause is "Allocating responsibilities" and addresses how the organization allocates responsibilities for the AI system across its lifecycle. The Crosswalk's vendor-onboarding row therefore anchors to A.10.3 (Suppliers); A.10.2 can also apply where supplier onboarding involves dividing responsibilities across teams. Reference: ISMS.online A.10.3 Suppliers.</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>NIST AI 100-1 Govern subcategory 6.1 = "Policies and procedures address AI risks from third-party entities." Govern 6.2 = "Contingency processes handle failures or incidents in third-party data or high-risk AI systems." Where the Govern Crosswalk maps internal reporting cadence to Govern 6.1 or stakeholder communication to Govern 6.2, the 6.x family's primary scope is third-party and contingency; broader stakeholder communication aligns with the Govern 5.x family ("Processes are in place for robust engagement with relevant AI actors") and reporting cadence within the organization aligns with Govern 1.x and 4.x. Rows that concern third-party / external-vendor contingencies map to the 6.x family; the internal reporting-cadence row maps to Govern 4.2 (impact communication).</t>
+          <t>NIST AI 100-1 Govern subcategory 6.1 = "Policies and procedures address AI risks from third-party entities." Govern 6.2 = "Contingency processes handle failures or incidents in third-party data or high-risk AI systems." The 6.x family's primary scope is third-party risk and contingency; broader stakeholder communication aligns with the Govern 5.x family ("Processes are in place for robust engagement with relevant AI actors") and reporting cadence within the organization aligns with Govern 1.x and 4.x. Rows that concern third-party / external-vendor contingencies map to the 6.x family; the internal reporting-cadence row maps to Govern 4.2 (impact communication).</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>Govern 1.4 = "Risk management process and outcomes are established through transparent policies, procedures, and other controls." Govern 1.5 = "Ongoing monitoring and periodic review of the risk management process and its outcomes are planned." Where the Crosswalk paraphrases Govern 1.4 as "evaluating effectiveness of AI risk management," the periodic-review framing aligns more precisely with Govern 1.5; both subcategories together cover policy + ongoing review.</t>
+          <t>Govern 1.4 = "Risk management process and outcomes are established through transparent policies, procedures, and other controls." Govern 1.5 = "Ongoing monitoring and periodic review of the risk management process and its outcomes are planned." The Crosswalk's failure-mode stress-test row therefore anchors to Govern 1.5 (periodic review of the risk-management process); 1.4 and 1.5 together cover policy plus ongoing review.</t>
         </is>
       </c>
     </row>
